--- a/storage/templates/requisicion.xlsx
+++ b/storage/templates/requisicion.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAX\Desktop\Documentos HOSPITAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sistema_hospital\storage\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B8B7351-36A8-4EBF-81CF-C0F55B807DEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD5F30BF-5C2F-4BF7-8534-28305FEE9160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -173,7 +173,7 @@
     <numFmt numFmtId="164" formatCode="&quot;Q&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_-[$Q-100A]* #,##0.00_-;\-[$Q-100A]* #,##0.00_-;_-[$Q-100A]* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -291,6 +291,19 @@
     </font>
     <font>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -500,18 +513,6 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -539,9 +540,6 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -562,37 +560,31 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -610,25 +602,46 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -987,21 +1000,21 @@
       <c r="D1" s="8"/>
     </row>
     <row r="2" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
     </row>
     <row r="3" spans="1:16" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
       <c r="E3" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="72" t="s">
+      <c r="F3" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="72"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="4" spans="1:16" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="11"/>
@@ -1029,34 +1042,34 @@
       <c r="G6" s="8"/>
     </row>
     <row r="7" spans="1:16" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="57" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="67"/>
-      <c r="C7" s="76" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="76"/>
+      <c r="D7" s="58"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
     </row>
     <row r="8" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A8" s="66" t="s">
+      <c r="A8" s="61" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="66"/>
-      <c r="C8" s="77" t="s">
+      <c r="B8" s="61"/>
+      <c r="C8" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="77"/>
+      <c r="D8" s="59"/>
       <c r="E8" s="8"/>
       <c r="F8" s="13"/>
       <c r="G8" s="13"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
     </row>
     <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.3">
       <c r="B9" s="33"/>
@@ -1069,39 +1082,39 @@
       <c r="I9" s="30"/>
     </row>
     <row r="10" spans="1:16" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="62" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
     </row>
     <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A11" s="58" t="s">
+      <c r="A11" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="48" t="s">
+      <c r="B11" s="66"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="K11" s="75"/>
-      <c r="L11" s="75"/>
-      <c r="M11" s="75"/>
-      <c r="N11" s="75"/>
-      <c r="O11" s="75"/>
-      <c r="P11" s="75"/>
+      <c r="E11" s="60"/>
+      <c r="F11" s="60"/>
+      <c r="G11" s="60"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
     </row>
     <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.3">
-      <c r="A12" s="43"/>
-      <c r="B12" s="43"/>
-      <c r="E12" s="47"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="E12" s="43"/>
       <c r="G12" s="9"/>
       <c r="K12" s="17"/>
       <c r="L12" s="17"/>
@@ -1113,8 +1126,8 @@
     <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.25">
       <c r="A13" s="23"/>
       <c r="B13" s="23"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="48"/>
       <c r="E13" s="16"/>
       <c r="F13" s="16"/>
       <c r="G13" s="16"/>
@@ -1126,14 +1139,14 @@
       <c r="P13" s="17"/>
     </row>
     <row r="14" spans="1:16" s="22" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="49" t="s">
+      <c r="A14" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="69" t="s">
+      <c r="B14" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="70"/>
-      <c r="D14" s="71"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="20" t="s">
         <v>1</v>
       </c>
@@ -1145,303 +1158,303 @@
       </c>
     </row>
     <row r="15" spans="1:16" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="38">
+      <c r="A15" s="71">
         <v>1</v>
       </c>
-      <c r="B15" s="63" t="s">
+      <c r="B15" s="72" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="64"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="39" t="s">
+      <c r="C15" s="73"/>
+      <c r="D15" s="74"/>
+      <c r="E15" s="75" t="s">
         <v>6</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41">
+      <c r="F15" s="76"/>
+      <c r="G15" s="77">
         <v>1625</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="38">
+      <c r="A16" s="71">
         <v>1</v>
       </c>
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="64"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="39" t="s">
+      <c r="C16" s="73"/>
+      <c r="D16" s="74"/>
+      <c r="E16" s="75" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41">
+      <c r="F16" s="76"/>
+      <c r="G16" s="77">
         <v>2380</v>
       </c>
     </row>
     <row r="17" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="38">
+      <c r="A17" s="71">
         <v>1</v>
       </c>
-      <c r="B17" s="63" t="s">
+      <c r="B17" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="64"/>
-      <c r="D17" s="65"/>
-      <c r="E17" s="39" t="s">
+      <c r="C17" s="73"/>
+      <c r="D17" s="74"/>
+      <c r="E17" s="75" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41">
+      <c r="F17" s="76"/>
+      <c r="G17" s="77">
         <v>2380</v>
       </c>
     </row>
     <row r="18" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="38">
+      <c r="A18" s="71">
         <v>1</v>
       </c>
-      <c r="B18" s="63" t="s">
+      <c r="B18" s="72" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="39" t="s">
+      <c r="C18" s="73"/>
+      <c r="D18" s="74"/>
+      <c r="E18" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41">
+      <c r="F18" s="76"/>
+      <c r="G18" s="77">
         <v>2380</v>
       </c>
     </row>
     <row r="19" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="38">
+      <c r="A19" s="71">
         <v>1</v>
       </c>
-      <c r="B19" s="63" t="s">
+      <c r="B19" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="64"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="39" t="s">
+      <c r="C19" s="73"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41">
+      <c r="F19" s="76"/>
+      <c r="G19" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="20" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="38">
+      <c r="A20" s="71">
         <v>1</v>
       </c>
-      <c r="B20" s="63" t="s">
+      <c r="B20" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C20" s="64"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="39" t="s">
+      <c r="C20" s="73"/>
+      <c r="D20" s="74"/>
+      <c r="E20" s="75" t="s">
         <v>12</v>
       </c>
-      <c r="F20" s="40"/>
-      <c r="G20" s="41">
+      <c r="F20" s="76"/>
+      <c r="G20" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="21" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="38">
+      <c r="A21" s="71">
         <v>1</v>
       </c>
-      <c r="B21" s="63" t="s">
+      <c r="B21" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="64"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="39" t="s">
+      <c r="C21" s="73"/>
+      <c r="D21" s="74"/>
+      <c r="E21" s="75" t="s">
         <v>13</v>
       </c>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41">
+      <c r="F21" s="76"/>
+      <c r="G21" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="38">
+      <c r="A22" s="71">
         <v>1</v>
       </c>
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="64"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="39" t="s">
+      <c r="C22" s="73"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41">
+      <c r="F22" s="76"/>
+      <c r="G22" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="23" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="38">
+      <c r="A23" s="71">
         <v>1</v>
       </c>
-      <c r="B23" s="63" t="s">
+      <c r="B23" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="64"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="39" t="s">
+      <c r="C23" s="73"/>
+      <c r="D23" s="74"/>
+      <c r="E23" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41">
+      <c r="F23" s="76"/>
+      <c r="G23" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="24" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="38">
+      <c r="A24" s="71">
         <v>1</v>
       </c>
-      <c r="B24" s="63" t="s">
+      <c r="B24" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="39" t="s">
+      <c r="C24" s="73"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41">
+      <c r="F24" s="76"/>
+      <c r="G24" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="25" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="38">
+      <c r="A25" s="71">
         <v>1</v>
       </c>
-      <c r="B25" s="63" t="s">
+      <c r="B25" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="64"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="39" t="s">
+      <c r="C25" s="73"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41">
+      <c r="F25" s="76"/>
+      <c r="G25" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="26" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="38">
+      <c r="A26" s="71">
         <v>1</v>
       </c>
-      <c r="B26" s="63" t="s">
+      <c r="B26" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="64"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="39" t="s">
+      <c r="C26" s="73"/>
+      <c r="D26" s="74"/>
+      <c r="E26" s="75" t="s">
         <v>18</v>
       </c>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41">
+      <c r="F26" s="76"/>
+      <c r="G26" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="27" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="38">
+      <c r="A27" s="71">
         <v>1</v>
       </c>
-      <c r="B27" s="63" t="s">
+      <c r="B27" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="64"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="39" t="s">
+      <c r="C27" s="73"/>
+      <c r="D27" s="74"/>
+      <c r="E27" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41">
+      <c r="F27" s="76"/>
+      <c r="G27" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="28" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="38">
+      <c r="A28" s="71">
         <v>1</v>
       </c>
-      <c r="B28" s="63" t="s">
+      <c r="B28" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="64"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="39" t="s">
+      <c r="C28" s="73"/>
+      <c r="D28" s="74"/>
+      <c r="E28" s="75" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41">
+      <c r="F28" s="76"/>
+      <c r="G28" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="29" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="38">
+      <c r="A29" s="71">
         <v>1</v>
       </c>
-      <c r="B29" s="63" t="s">
+      <c r="B29" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="64"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="39" t="s">
+      <c r="C29" s="73"/>
+      <c r="D29" s="74"/>
+      <c r="E29" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="40"/>
-      <c r="G29" s="41">
+      <c r="F29" s="76"/>
+      <c r="G29" s="77">
         <v>1550</v>
       </c>
     </row>
     <row r="30" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="38">
+      <c r="A30" s="71">
         <v>1</v>
       </c>
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="39" t="s">
+      <c r="C30" s="73"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="75" t="s">
         <v>24</v>
       </c>
-      <c r="F30" s="40"/>
-      <c r="G30" s="41">
+      <c r="F30" s="76"/>
+      <c r="G30" s="77">
         <v>1420</v>
       </c>
     </row>
     <row r="31" spans="1:7" s="22" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="38">
+      <c r="A31" s="71">
         <v>1</v>
       </c>
-      <c r="B31" s="63" t="s">
+      <c r="B31" s="72" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="64"/>
-      <c r="D31" s="65"/>
-      <c r="E31" s="39" t="s">
+      <c r="C31" s="73"/>
+      <c r="D31" s="74"/>
+      <c r="E31" s="75" t="s">
         <v>25</v>
       </c>
-      <c r="F31" s="40"/>
-      <c r="G31" s="41">
+      <c r="F31" s="76"/>
+      <c r="G31" s="77">
         <v>1420</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="7"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="52" t="s">
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="47" t="s">
         <v>38</v>
       </c>
-      <c r="G32" s="51">
+      <c r="G32" s="78">
         <f>SUM(G15:G31)</f>
         <v>28655</v>
       </c>
@@ -1452,13 +1465,13 @@
     <row r="34" spans="1:10" ht="15" x14ac:dyDescent="0.3">
       <c r="C34" s="37"/>
       <c r="D34" s="37"/>
-      <c r="G34" s="42"/>
+      <c r="G34" s="38"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B35" s="59"/>
+      <c r="B35" s="67"/>
       <c r="D35" s="14" t="s">
         <v>32</v>
       </c>
@@ -1467,37 +1480,37 @@
       <c r="H35" s="3"/>
     </row>
     <row r="36" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="55"/>
-      <c r="E36" s="54"/>
+      <c r="A36" s="50"/>
+      <c r="E36" s="49"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
     </row>
     <row r="37" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="32"/>
-      <c r="B37" s="60" t="s">
+      <c r="B37" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="60"/>
+      <c r="C37" s="68"/>
       <c r="D37" s="30"/>
-      <c r="E37" s="60" t="s">
+      <c r="E37" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="F37" s="60"/>
-      <c r="G37" s="60"/>
+      <c r="F37" s="68"/>
+      <c r="G37" s="68"/>
       <c r="H37" s="1"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B38" s="61" t="s">
+      <c r="B38" s="69" t="s">
         <v>26</v>
       </c>
-      <c r="C38" s="61"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="78" t="s">
+      <c r="C38" s="69"/>
+      <c r="D38" s="51"/>
+      <c r="E38" s="70" t="s">
         <v>4</v>
       </c>
-      <c r="F38" s="78"/>
-      <c r="G38" s="78"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
     </row>
     <row r="39" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
@@ -1512,11 +1525,11 @@
       <c r="G40" s="6"/>
     </row>
     <row r="41" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="57"/>
-      <c r="E41" s="57"/>
+      <c r="A41" s="66"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="48"/>
+      <c r="D41" s="52"/>
+      <c r="E41" s="52"/>
       <c r="F41" s="4"/>
       <c r="G41" s="4"/>
       <c r="H41" s="6"/>
@@ -1532,20 +1545,20 @@
       <c r="H43" s="16"/>
     </row>
     <row r="44" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="73"/>
-      <c r="C44" s="73"/>
-      <c r="D44" s="73"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="73"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="54"/>
+      <c r="F44" s="54"/>
       <c r="G44" s="25"/>
       <c r="H44" s="16"/>
     </row>
     <row r="45" spans="1:10" ht="15" x14ac:dyDescent="0.3">
-      <c r="B45" s="74"/>
-      <c r="C45" s="74"/>
-      <c r="D45" s="74"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
+      <c r="B45" s="55"/>
+      <c r="C45" s="55"/>
+      <c r="D45" s="55"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
       <c r="G45" s="16"/>
       <c r="H45" s="16"/>
       <c r="I45" s="26"/>
@@ -1670,6 +1683,27 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E37:G37"/>
+    <mergeCell ref="E38:G38"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="A11:B11"/>
     <mergeCell ref="F3:G3"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B45:F45"/>
@@ -1686,27 +1720,6 @@
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="E11:G11"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E37:G37"/>
-    <mergeCell ref="E38:G38"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
